--- a/data/trans_orig/P79A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34360</t>
+          <t>50192</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>56449</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>42880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>74652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>491173</t>
+          <t>546499</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480578</t>
+          <t>528337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498882</t>
+          <t>557435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>732917</t>
+          <t>797618</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>723453</t>
+          <t>787048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>739410</t>
+          <t>805378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1224091</t>
+          <t>1344118</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1209653</t>
+          <t>1325915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1235839</t>
+          <t>1357687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>50966</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>71977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46236</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69507</t>
+          <t>72283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92254</t>
+          <t>104714</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67348</t>
+          <t>83568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123438</t>
+          <t>130693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2244309</t>
+          <t>2179600</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2222883</t>
+          <t>2158589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2261917</t>
+          <t>2193608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2191587</t>
+          <t>2117644</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2168316</t>
+          <t>2099109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2207211</t>
+          <t>2132140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4435896</t>
+          <t>4297245</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4404712</t>
+          <t>4271266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4460802</t>
+          <t>4318391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645253</t>
+          <t>709221</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640195</t>
+          <t>704307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>655091</t>
+          <t>728765</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648721</t>
+          <t>720685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658567</t>
+          <t>732485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1300343</t>
+          <t>1437986</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1291789</t>
+          <t>1429738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1303944</t>
+          <t>1442813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>65370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98092</t>
+          <t>111975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99043</t>
+          <t>104829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114847</t>
+          <t>141544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175348</t>
+          <t>201772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3380736</t>
+          <t>3435321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3353797</t>
+          <t>3408708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399836</t>
+          <t>3455313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3579595</t>
+          <t>3644028</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3554751</t>
+          <t>3623478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3597608</t>
+          <t>3660814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6960331</t>
+          <t>7079349</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6930335</t>
+          <t>7047218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6990836</t>
+          <t>7107446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
